--- a/Docs/GameDesign_Videojuego.xlsx
+++ b/Docs/GameDesign_Videojuego.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr showInkAnnotation="0"/>
-  <xr:revisionPtr revIDLastSave="162" documentId="7_{CBDD559A-4AD0-044A-8E74-3265AD4CF6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6FDD4B2-85B4-44D7-A08C-35B572DF5943}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario_local\Documents\Space_Station\Docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F286CD23-F03C-49A3-9D10-7BBF28087857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -22,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="51">
   <si>
     <t>Valores</t>
   </si>
@@ -45,9 +48,6 @@
     <t>Num. mundos</t>
   </si>
   <si>
-    <t>Niveles/mundo</t>
-  </si>
-  <si>
     <t>ALTA</t>
   </si>
   <si>
@@ -81,12 +81,6 @@
     <t>Estandarte</t>
   </si>
   <si>
-    <t>Robot movil</t>
-  </si>
-  <si>
-    <t>Robot estático</t>
-  </si>
-  <si>
     <t>Miniboss</t>
   </si>
   <si>
@@ -103,6 +97,96 @@
   </si>
   <si>
     <t>Cadencia de disparo</t>
+  </si>
+  <si>
+    <t>Características enemigos MUNDO 1</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>ESTATICO</t>
+  </si>
+  <si>
+    <t>SEGUIR</t>
+  </si>
+  <si>
+    <t>ALEJARSE</t>
+  </si>
+  <si>
+    <t>Niveles por mundo</t>
+  </si>
+  <si>
+    <t>Características enemigos MUNDO 2</t>
+  </si>
+  <si>
+    <t>Características enemigos MUNDO 3</t>
+  </si>
+  <si>
+    <t>Robot kamikaze</t>
+  </si>
+  <si>
+    <t>Robot táctico</t>
+  </si>
+  <si>
+    <t>Rango</t>
+  </si>
+  <si>
+    <t>RANDOM</t>
+  </si>
+  <si>
+    <t>PATRULLA</t>
+  </si>
+  <si>
+    <t>Robot patrulla</t>
+  </si>
+  <si>
+    <t>Jugador</t>
+  </si>
+  <si>
+    <t>Velocidad</t>
+  </si>
+  <si>
+    <t>Cadencia</t>
+  </si>
+  <si>
+    <t>Pistola base</t>
+  </si>
+  <si>
+    <t>50-20</t>
+  </si>
+  <si>
+    <t>60-40</t>
+  </si>
+  <si>
+    <t>70-80</t>
+  </si>
+  <si>
+    <t>Nos soporta x golpes</t>
+  </si>
+  <si>
+    <t>1-2 MB</t>
+  </si>
+  <si>
+    <t>4-5 B</t>
+  </si>
+  <si>
+    <t>10 M</t>
+  </si>
+  <si>
+    <t>30 A</t>
+  </si>
+  <si>
+    <t>60 M</t>
+  </si>
+  <si>
+    <t>BAJA - 5</t>
+  </si>
+  <si>
+    <t>MEDIA - 300</t>
+  </si>
+  <si>
+    <t>Jugador(Vida-Escudo)</t>
   </si>
 </sst>
 </file>
@@ -124,7 +208,7 @@
       <family val="18"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,8 +245,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -220,32 +316,6 @@
       <top style="medium">
         <color rgb="FF505050"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF505050"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF505050"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF505050"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF505050"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF505050"/>
-      </top>
       <bottom style="medium">
         <color rgb="FF505050"/>
       </bottom>
@@ -262,41 +332,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF505050"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF505050"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -320,28 +355,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -350,19 +363,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -406,11 +406,24 @@
     </border>
     <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -419,19 +432,138 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -440,19 +572,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -464,10 +596,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -476,41 +620,2257 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="319">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE97132"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF47D359"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD86DCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -550,6 +2910,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00FF00"/>
       <color rgb="FFE97132"/>
       <color rgb="FFFFFF00"/>
       <color rgb="FF47D359"/>
@@ -884,275 +3245,1191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C80C395-E99E-2745-BAA8-AB83A008BA5B}">
-  <dimension ref="B2:O18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:R40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.25" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="5" width="16.75" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="14.75" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="12" max="12" width="11.125" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15">
-      <c r="J2" s="22" t="s">
+    <row r="1" spans="2:18" ht="15" thickBot="1"/>
+    <row r="2" spans="2:18" ht="15" thickBot="1">
+      <c r="J2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
+      <c r="K2" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="2:15">
-      <c r="J3" s="27" t="s">
+    <row r="3" spans="2:18" ht="15" thickBot="1">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
+      <c r="I3">
+        <f>K12/H3</f>
+        <v>70</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="2:15">
-      <c r="B4" s="7"/>
+    <row r="4" spans="2:18" ht="15" thickBot="1">
+      <c r="B4" s="5"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="25"/>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <f>K12/H4</f>
+        <v>35</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="2:18">
+      <c r="B5" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-    </row>
-    <row r="5" spans="2:15">
-      <c r="B5" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="2">
         <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <f>K12/H5</f>
+        <v>14</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="B6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <f xml:space="preserve"> C5 /D6</f>
         <v>30</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>3</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="24" t="s">
+      <c r="E6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="24"/>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <f>K12/H6</f>
         <v>10</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
+      <c r="J6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="2:15">
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5">
+    <row r="7" spans="2:18" ht="15" thickBot="1">
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4">
         <f xml:space="preserve"> C6 /E7</f>
         <v>10</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="F7" s="25"/>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <f>K12/H7</f>
+        <v>7</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="9" spans="2:18" ht="15" thickBot="1"/>
+    <row r="10" spans="2:18" ht="15" thickBot="1">
+      <c r="B10" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="31"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+    </row>
+    <row r="11" spans="2:18">
+      <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="C11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="11" t="s">
+    <row r="12" spans="2:18">
+      <c r="B12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="37"/>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
+      <c r="B14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="B15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="15" thickBot="1">
+      <c r="B16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" thickBot="1">
+      <c r="B17" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="B18" s="7"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="27"/>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+      <c r="N18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" thickBot="1">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="L19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+      <c r="N19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickBot="1">
+      <c r="B20" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="31"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="E21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="H21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="7"/>
+      <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="C22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="C23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="7"/>
+      <c r="B24" s="10" t="s">
         <v>19</v>
       </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J24" s="7"/>
     </row>
-    <row r="12" spans="2:15">
-      <c r="B12" s="19" t="s">
+    <row r="25" spans="1:14">
+      <c r="A25" s="7"/>
+      <c r="B25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" thickBot="1">
+      <c r="A26" s="7"/>
+      <c r="B26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="20" t="s">
-        <v>5</v>
-      </c>
+      <c r="C26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="7"/>
     </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="17" t="s">
-        <v>5</v>
-      </c>
+    <row r="27" spans="1:14" ht="15" thickBot="1">
+      <c r="A27" s="7"/>
+      <c r="B27" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="7"/>
     </row>
-    <row r="14" spans="2:15">
-      <c r="B14" s="19" t="s">
+    <row r="28" spans="1:14">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" thickBot="1">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1">
+      <c r="A30" s="7"/>
+      <c r="B30" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="7"/>
+      <c r="B31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="7"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="7"/>
+      <c r="B32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="7"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="7"/>
+      <c r="B34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="7"/>
+      <c r="B35" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="1:11" ht="15" thickBot="1">
+      <c r="A36" s="7"/>
+      <c r="B36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37" spans="1:11" ht="15" thickBot="1">
+      <c r="A37" s="7"/>
+      <c r="B37" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="20"/>
+      <c r="C37" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="7"/>
     </row>
-    <row r="15" spans="2:15">
-      <c r="B15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="18"/>
+    <row r="38" spans="1:11">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
     </row>
-    <row r="16" spans="2:15">
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+    <row r="39" spans="1:11">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
+    <row r="40" spans="1:11">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C12:H15">
+  <mergeCells count="4">
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B30:I30"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:H16 J12:J13">
+    <cfRule type="cellIs" dxfId="318" priority="323" operator="equal">
+      <formula>"MUY ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:H16 J12:J13">
+    <cfRule type="cellIs" dxfId="317" priority="322" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:H16 J12:J13">
+    <cfRule type="cellIs" dxfId="316" priority="321" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:H16 J12:J13">
+    <cfRule type="cellIs" dxfId="315" priority="320" operator="equal">
+      <formula>"BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:H16 J12:J13">
+    <cfRule type="cellIs" dxfId="314" priority="319" operator="equal">
+      <formula>"MUY BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="cellIs" dxfId="303" priority="304" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="cellIs" dxfId="302" priority="303" operator="equal">
+      <formula>"SEGUIR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="cellIs" dxfId="301" priority="302" operator="equal">
+      <formula>"ALEJARSE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="cellIs" dxfId="135" priority="136" operator="equal">
+      <formula>"ALEJARSE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="cellIs" dxfId="134" priority="135" operator="equal">
+      <formula>"SEGUIR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17">
+    <cfRule type="cellIs" dxfId="132" priority="133" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="cellIs" dxfId="131" priority="132" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I16">
+    <cfRule type="cellIs" dxfId="130" priority="131" operator="equal">
+      <formula>"MUY ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I16">
+    <cfRule type="cellIs" dxfId="129" priority="130" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I16">
+    <cfRule type="cellIs" dxfId="128" priority="129" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I16">
+    <cfRule type="cellIs" dxfId="127" priority="128" operator="equal">
+      <formula>"BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I16">
+    <cfRule type="cellIs" dxfId="126" priority="127" operator="equal">
+      <formula>"MUY BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="cellIs" dxfId="62" priority="63" operator="equal">
+      <formula>"SEGUIR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:H26">
+    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+      <formula>"MUY ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:H26">
+    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:H26">
+    <cfRule type="cellIs" dxfId="29" priority="30" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:H26">
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+      <formula>"BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:H26">
+    <cfRule type="cellIs" dxfId="27" priority="28" operator="equal">
+      <formula>"MUY BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
+      <formula>"ALEJARSE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27">
+    <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
+      <formula>"SEGUIR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27">
+    <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27">
+    <cfRule type="cellIs" dxfId="23" priority="24" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I26">
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
+      <formula>"MUY ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I26">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I26">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I26">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+      <formula>"BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I26">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
+      <formula>"MUY BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
+      <formula>"SEGUIR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:H36">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"MUY ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:H36">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:H36">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:H36">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:H36">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+      <formula>"MUY BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"ALEJARSE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"SEGUIR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"ESTATICO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I36">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"MUY ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I36">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I36">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I36">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"MUY ALTA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:H15">
+      <formula>"BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I36">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"ALTA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:H15">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"MEDIA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:H15">
+      <formula>"MUY BAJA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"BAJA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:H15">
+      <formula>"ALEJARSE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"MUY BAJA"</formula>
+      <formula>"SEGUIR"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:H15" xr:uid="{B381B63F-1474-4271-8762-50E626F7DB47}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:I16 C22:I26 C32:I36" xr:uid="{2C9241D9-FAF3-4923-88B4-06DF4384620B}">
       <formula1>$J$3:$J$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>